--- a/Data_Folder/Contact_Data.xlsx
+++ b/Data_Folder/Contact_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bssuniversal-my.sharepoint.com/personal/amyma_usman_bssuniversal_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AmymaUsman\PycharmProjects\SmartCRM_Automation\Data_Folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{7FF76E00-840D-4307-86F7-74C5CCED1349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9288047F-AA0E-4FEF-831C-F3661126FA7B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF72A8A3-93D9-4E1E-BE67-4FBB520478F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{FC4AE605-A8B6-406B-867D-C86ACDE0851C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>${TITLE_FIELD_TEXT}</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t>Finance</t>
+  </si>
+  <si>
+    <t>${ACCOUNT_NAME_TEXT}</t>
+  </si>
+  <si>
+    <t>Test Lead</t>
   </si>
 </sst>
 </file>
@@ -511,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D1A839D-098A-44CD-B2AC-67E2650B8C8C}">
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -523,20 +529,21 @@
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="26.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="26.140625" customWidth="1"/>
-    <col min="12" max="12" width="23.85546875" customWidth="1"/>
-    <col min="13" max="13" width="26.7109375" customWidth="1"/>
-    <col min="14" max="14" width="26.5703125" customWidth="1"/>
-    <col min="15" max="15" width="30.28515625" customWidth="1"/>
-    <col min="16" max="16" width="28.85546875" customWidth="1"/>
-    <col min="17" max="18" width="31" customWidth="1"/>
-    <col min="19" max="19" width="33.7109375" customWidth="1"/>
-    <col min="20" max="20" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25" customWidth="1"/>
+    <col min="10" max="10" width="26.7109375" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="12" width="26.140625" customWidth="1"/>
+    <col min="13" max="13" width="23.85546875" customWidth="1"/>
+    <col min="14" max="14" width="26.7109375" customWidth="1"/>
+    <col min="15" max="15" width="26.5703125" customWidth="1"/>
+    <col min="16" max="16" width="30.28515625" customWidth="1"/>
+    <col min="17" max="17" width="28.85546875" customWidth="1"/>
+    <col min="18" max="19" width="31" customWidth="1"/>
+    <col min="20" max="20" width="33.7109375" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,40 +572,43 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -627,36 +637,39 @@
         <v>24</v>
       </c>
       <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>58</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>3535242443</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>71</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>3443535456</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>21</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>8394892842</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>28</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>29</v>
       </c>
     </row>
